--- a/ig/DM-DECEMBRE-2024/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -9511,7 +9511,7 @@
     <t>1454</t>
   </si>
   <si>
-    <t>Evaluation et suivi standardisé des commotions cérébrales</t>
+    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL)</t>
   </si>
   <si>
     <t>1455</t>
